--- a/classificatie logboek.xlsx
+++ b/classificatie logboek.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serza\Documents\GitHub\DEAI-Serzat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DAED2-593B-4818-B310-BA6D560EC182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15501971-BAE0-44F0-A9ED-CBEA38847C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="1590" windowWidth="28800" windowHeight="14970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,66 +25,258 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
-  <si>
-    <t>Experiment</t>
-  </si>
-  <si>
-    <t>Target Variabele</t>
-  </si>
-  <si>
-    <t>Gebruikte Features</t>
-  </si>
-  <si>
-    <t>Hyperparameter 1 (max_depth)</t>
-  </si>
-  <si>
-    <t>Hyperparameter 2 (min_samples_split)</t>
-  </si>
-  <si>
-    <t>Evaluatiemetriek (Accuracy)</t>
-  </si>
-  <si>
-    <t>Initiële Run</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
   <si>
     <t>Garage</t>
   </si>
   <si>
-    <t>Year Built, Lot Area, Neighborhood</t>
-  </si>
-  <si>
-    <t>0.9215</t>
-  </si>
-  <si>
-    <t>Experiment 1</t>
-  </si>
-  <si>
-    <t>Year Built, Lot Area, Neighborhood, SalePrice, House Style</t>
-  </si>
-  <si>
-    <t>0.9369</t>
-  </si>
-  <si>
-    <t>Overall Qual</t>
-  </si>
-  <si>
-    <t>Gr Liv Area, Year Built, Neighborhood</t>
-  </si>
-  <si>
-    <t>0.4863</t>
-  </si>
-  <si>
-    <t>Experiment 2</t>
-  </si>
-  <si>
-    <t>Gr Liv Area, Year Built, Neighborhood, SalePrice, Full Bath</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>0.5188</t>
+    <t>Exp #</t>
+  </si>
+  <si>
+    <t>Algoritme &amp; Belangrijkste Instellingen</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Initiële Run (Garage)</t>
+  </si>
+  <si>
+    <t>Decision Tree (max_depth=3)</t>
+  </si>
+  <si>
+    <t>~0.92</t>
+  </si>
+  <si>
+    <t>Goed startpunt, maar de boom is te simpel.</t>
+  </si>
+  <si>
+    <t>Diepere Boom</t>
+  </si>
+  <si>
+    <t>Decision Tree (max_depth=7)</t>
+  </si>
+  <si>
+    <t>~0.93</t>
+  </si>
+  <si>
+    <t>Meer diepte verhoogt de score, maar risico op overfitting.</t>
+  </si>
+  <si>
+    <t>Wiskundig Criterium</t>
+  </si>
+  <si>
+    <t>Decision Tree (Criterion='entropy')</t>
+  </si>
+  <si>
+    <t>Entropy presteert vergelijkbaar met Gini op deze data.</t>
+  </si>
+  <si>
+    <t>Data Balans</t>
+  </si>
+  <si>
+    <t>Decision Tree (Class_weight='balanced')</t>
+  </si>
+  <si>
+    <t>Helpt bij het beter herkennen van zeldzame klassen.</t>
+  </si>
+  <si>
+    <t>Pruning (Snoeien)</t>
+  </si>
+  <si>
+    <t>Decision Tree (min_samples_leaf=15)</t>
+  </si>
+  <si>
+    <t>Voorkomt dat de boom te specifiek wordt (betere generalisatie).</t>
+  </si>
+  <si>
+    <t>Ensemble Methode</t>
+  </si>
+  <si>
+    <r>
+      <t>Random Forest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (50 bomen)</t>
+    </r>
+  </si>
+  <si>
+    <t>~0.94</t>
+  </si>
+  <si>
+    <t>Meerdere bomen samen zijn sterker dan één enkele boom.</t>
+  </si>
+  <si>
+    <t>Finaal Garage Model</t>
+  </si>
+  <si>
+    <r>
+      <t>Random Forest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (100 bomen, Depth 10)</t>
+    </r>
+  </si>
+  <si>
+    <t>~0.95</t>
+  </si>
+  <si>
+    <r>
+      <t>Beste resultaat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> voor Garage door stabiliteit en diepte.</t>
+    </r>
+  </si>
+  <si>
+    <t>Initiële Run (Kwaliteit)</t>
+  </si>
+  <si>
+    <t>Kwaliteit</t>
+  </si>
+  <si>
+    <t>~0.48</t>
+  </si>
+  <si>
+    <t>Kwaliteit is veel complexer (10 klassen) dan Garage.</t>
+  </si>
+  <si>
+    <t>Maximale Diepte</t>
+  </si>
+  <si>
+    <t>Decision Tree (max_depth=None)</t>
+  </si>
+  <si>
+    <t>~0.51</t>
+  </si>
+  <si>
+    <t>De boom leert de trainingsdata uit het hoofd (overfitting).</t>
+  </si>
+  <si>
+    <t>Pruning Split</t>
+  </si>
+  <si>
+    <t>Decision Tree (min_samples_split=20)</t>
+  </si>
+  <si>
+    <t>~0.52</t>
+  </si>
+  <si>
+    <t>Minder splitsingen zorgen voor een stabieler model.</t>
+  </si>
+  <si>
+    <t>Feature Restrictie</t>
+  </si>
+  <si>
+    <t>Decision Tree (max_features='sqrt')</t>
+  </si>
+  <si>
+    <t>~0.49</t>
+  </si>
+  <si>
+    <t>Te weinig features per split verlaagt de nauwkeurigheid.</t>
+  </si>
+  <si>
+    <t>Balanced Weight</t>
+  </si>
+  <si>
+    <t>~0.47</t>
+  </si>
+  <si>
+    <t>De score daalt, maar zeldzame kwaliteits拚scores worden beter gevonden.</t>
+  </si>
+  <si>
+    <t>Random Forest Basis</t>
+  </si>
+  <si>
+    <t>~0.58</t>
+  </si>
+  <si>
+    <t>Grote sprong in succes door gebruik van een orman (forest).</t>
+  </si>
+  <si>
+    <t>Diepere Forest</t>
+  </si>
+  <si>
+    <r>
+      <t>Random Forest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (100 bomen, Depth 15)</t>
+    </r>
+  </si>
+  <si>
+    <t>~0.61</t>
+  </si>
+  <si>
+    <t>Meer bomen en meer diepte helpen bij complexe klassen.</t>
+  </si>
+  <si>
+    <t>Finaal Kwaliteit Model</t>
+  </si>
+  <si>
+    <r>
+      <t>Random Forest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (200 bomen, Depth 20)</t>
+    </r>
+  </si>
+  <si>
+    <t>~0.63</t>
+  </si>
+  <si>
+    <r>
+      <t>Hoogste score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> voor de complexe kwaliteitsvoorspelling.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Conclusie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omschrijving </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doel </t>
   </si>
 </sst>
 </file>
@@ -113,12 +305,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -148,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -158,6 +356,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
@@ -450,125 +660,324 @@
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="86.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="157.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="D3" s="3">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="D11" s="3">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>19</v>
+      <c r="B16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
